--- a/internship_application_form_templates/014_public_health_informatics_fellowship_application--internship_application_form_templates.xlsx
+++ b/internship_application_form_templates/014_public_health_informatics_fellowship_application--internship_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>public_health</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Public Health</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>data_analysis</t>
+          <t>programming</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Data Analysis</t>
+          <t>Programming</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>programming</t>
+          <t>data_mining</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Programming</t>
+          <t>Data Mining</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>data_mining</t>
+          <t>machine_learning</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Data Mining</t>
+          <t>Machine Learning</t>
         </is>
       </c>
     </row>
@@ -1241,27 +1241,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>machine_learning</t>
+          <t>data_visualization</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>Machine Learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>motivation_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>data_visualization</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>Data Visualization</t>
         </is>
